--- a/data/chinese/P3T1_Chapter1.xlsx
+++ b/data/chinese/P3T1_Chapter1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/ChineseLearning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E9603B-BF22-AF47-BE21-F1DC398593A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A45AEF-8CB6-4740-862B-836BEDB161EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -65,16 +65,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>危樓高百尺，_x0015_
+    <t>危樓高百尺，
 手可摘星辰。
 不敢高聲語，
 恐驚天上人。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">【解釋】：詩人住在山頂的高樓上，感覺樓實在太高了，離天空很近，彷彿一抬手就能摸到星星。他小心翼翼不敢大聲說話，生怕打擾到天上的仙人。
-【簡單中心思想】：詩人透過奇妙的想像，寫出山樓的雄偉高聳，也表達出驚訝、讚嘆的心情。
-</t>
+    <t>【解釋】：詩人住在山頂的高樓上，感覺樓實在太高了，離天空很近，彷彿一抬手就能摸到星星。他小心翼翼不敢大聲說話，生怕打擾到天上的仙人。
+【簡單中心思想】：詩人透過奇妙的想像，寫出山樓的雄偉高聳，也表達出驚訝、讚嘆的心情。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1042,7 +1041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="112">
+    <row r="2" spans="1:3" ht="96">
       <c r="A2" t="s">
         <v>8</v>
       </c>
